--- a/data/billable_charges_CTS.xlsx
+++ b/data/billable_charges_CTS.xlsx
@@ -97299,13 +97299,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7FE7A10-5D3A-45BB-BFF6-CEC5D96F8ADB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64D129FC-1549-4231-BA83-988D34E269D1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B8B2B06-20E3-4A13-8914-D8964D057746}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3B86A68-055A-4AAE-BFB2-B2C093A5581C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{778DA287-12AF-420F-84B4-60DDF5232026}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB8DED7E-4926-48FD-B406-47B9A65471F7}"/>
 </file>
--- a/data/billable_charges_CTS.xlsx
+++ b/data/billable_charges_CTS.xlsx
@@ -98582,13 +98582,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A51D0E7A-96BA-4D4A-AAB5-3DA31036467C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{466B3F40-D4DD-4195-9DCE-B8B348C7CCAD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCA5659C-6A93-4B2E-986D-23D41A0F9E51}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6365A450-1CE5-4DA1-AA00-3B098374D305}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8B709E6-3609-4517-8159-711F94692298}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C6CC213-6799-49C9-BF23-0369E9367DF6}"/>
 </file>
--- a/data/billable_charges_CTS.xlsx
+++ b/data/billable_charges_CTS.xlsx
@@ -98582,13 +98582,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{466B3F40-D4DD-4195-9DCE-B8B348C7CCAD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C5209F2-8753-46A1-8693-FB41FE3D566A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6365A450-1CE5-4DA1-AA00-3B098374D305}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56DA3D68-284B-411F-A6BC-C3BEADBBB44B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C6CC213-6799-49C9-BF23-0369E9367DF6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95C1FD77-1809-4381-B0D0-273B59305349}"/>
 </file>
--- a/data/billable_charges_CTS.xlsx
+++ b/data/billable_charges_CTS.xlsx
@@ -97344,13 +97344,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B00F313-AD65-4C0C-80AB-1574557BE500}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B2130F5-8634-40ED-B068-1E6768E21161}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74E59585-6C90-4EAC-9B68-722653B74472}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3096FA9-C21E-489A-8445-80689171DAFC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{131E99B6-1C14-418A-9B9E-FB057AA2F1FE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{16651AA2-8CAE-4E5B-8582-B199BA0A546A}"/>
 </file>
--- a/data/billable_charges_CTS.xlsx
+++ b/data/billable_charges_CTS.xlsx
@@ -98590,13 +98590,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5EEC4096-871A-459E-A6F6-426DA6872560}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E8CAC96-9C70-4174-9B5E-A40E4318B5C8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41830D59-4A72-494F-BCC4-DBB3B0CF8E22}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F99664E-FA54-4D0C-B615-91B70169C5AB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6E50139-0ACF-432A-9B4B-7B8296ECEBAC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E664D5C7-DA32-49B6-9785-E2D520A87A8B}"/>
 </file>
--- a/data/billable_charges_CTS.xlsx
+++ b/data/billable_charges_CTS.xlsx
@@ -98590,13 +98590,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E8CAC96-9C70-4174-9B5E-A40E4318B5C8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63C26841-C58E-4ADA-8C03-F4C03CE048FF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F99664E-FA54-4D0C-B615-91B70169C5AB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{640D7B2D-1D6C-42E9-B132-0CEA0E35F1C8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E664D5C7-DA32-49B6-9785-E2D520A87A8B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B459302D-4A56-4B6E-8603-093A08727D82}"/>
 </file>
--- a/data/billable_charges_CTS.xlsx
+++ b/data/billable_charges_CTS.xlsx
@@ -97526,13 +97526,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC4E036D-5890-4892-AB46-6A77208C5596}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFB02EF6-A309-4E56-B48D-8B0CFD0A6B32}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{054C4D40-3F64-4411-B3CB-55F5511651EF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7F3A13C-EA4F-4A7F-8BCF-6E7EB61A9CAF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB1C19A5-7325-4F8C-BC6E-217C5153F594}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06F62A64-FD05-486D-9E02-E6E53900779F}"/>
 </file>
--- a/data/billable_charges_CTS.xlsx
+++ b/data/billable_charges_CTS.xlsx
@@ -98485,13 +98485,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07154974-8F83-40EA-881E-9E29F11307A1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61A37FFA-2679-47B5-ADBE-3DBF70015ECF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B84300B-F813-4FF1-82A8-C31BC511FE0E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A5B17C5-EFC9-4E74-819E-A0067B79EBEA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25A39ECF-5E3A-414A-8632-DB7B8A4CF70A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B9F9520-60EB-4264-8282-25279546A1FA}"/>
 </file>
--- a/data/billable_charges_CTS.xlsx
+++ b/data/billable_charges_CTS.xlsx
@@ -98485,13 +98485,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61A37FFA-2679-47B5-ADBE-3DBF70015ECF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC878785-BEBF-4339-9992-65E41CD76915}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A5B17C5-EFC9-4E74-819E-A0067B79EBEA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{129BAB8B-A02B-4ACC-AE3D-012F14BDA5AC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B9F9520-60EB-4264-8282-25279546A1FA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F44285DA-43D5-4282-9BEC-D2F10863E732}"/>
 </file>